--- a/tools/夏祭り売上_合算テンプレート.xlsx
+++ b/tools/夏祭り売上_合算テンプレート.xlsx
@@ -18,12 +18,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="&quot;¥&quot;#,##0"/>
     <numFmt numFmtId="165" formatCode="#,##0&quot;件&quot;"/>
     <numFmt numFmtId="166" formatCode="#,##0&quot;行&quot;"/>
+    <numFmt numFmtId="167" formatCode="#,##0&quot;枚&quot;"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -102,6 +103,12 @@
       <name val="Arial"/>
       <i val="1"/>
       <color rgb="0086868B"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="006D28D9"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -154,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -181,6 +188,8 @@
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -546,7 +555,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D18"/>
+  <dimension ref="B2:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -685,8 +694,26 @@
         <v/>
       </c>
     </row>
+    <row r="17">
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>商品券の使用枚数（換金用）</t>
+        </is>
+      </c>
+      <c r="C17" s="23">
+        <f>SUMPRODUCT((貼り付け!$K$2:$K$5000="有効")*(貼り付け!$M$2:$M$5000)/COUNTIFS(貼り付け!$A$2:$A$5000,貼り付け!$A$2:$A$5000&amp;""))</f>
+        <v/>
+      </c>
+    </row>
     <row r="18">
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>※ 商品券は売上に含まれています（後で換金されるため）。枚数は換金額の確認用です。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>※ 各iPadの「履歴・集計」画面の総売上を足した金額と、上の総売上が一致するか必ず確認してください。</t>
         </is>
@@ -948,7 +975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -963,6 +990,7 @@
     <col width="11" customWidth="1" min="10" max="10"/>
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1026,6 +1054,11 @@
           <t>登録時刻</t>
         </is>
       </c>
+      <c r="M1" s="20" t="inlineStr">
+        <is>
+          <t>商品券</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21" t="inlineStr">

--- a/tools/夏祭り売上_合算テンプレート.xlsx
+++ b/tools/夏祭り売上_合算テンプレート.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="166" formatCode="#,##0&quot;行&quot;"/>
     <numFmt numFmtId="167" formatCode="#,##0&quot;枚&quot;"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -109,6 +109,24 @@
       <name val="Arial"/>
       <b val="1"/>
       <color rgb="006D28D9"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00C62828"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00E8590C"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001D1D1F"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -161,7 +179,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -190,6 +208,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -555,7 +578,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:D19"/>
+  <dimension ref="B2:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -706,16 +729,45 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>PayPay支払いの合計</t>
+        </is>
+      </c>
+      <c r="C18" s="25">
+        <f>SUMPRODUCT((貼り付け!$K$2:$K$5000="有効")*(貼り付け!$N$2:$N$5000="PayPay")*(貼り付け!$H$2:$H$5000)/COUNTIFS(貼り付け!$A$2:$A$5000,貼り付け!$A$2:$A$5000&amp;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>未納（職員販売・回収前）の合計</t>
+        </is>
+      </c>
+      <c r="C19" s="27">
+        <f>SUMPRODUCT((貼り付け!$K$2:$K$5000="有効")*(貼り付け!$N$2:$N$5000="未納")*(貼り付け!$H$2:$H$5000)/COUNTIFS(貼り付け!$A$2:$A$5000,貼り付け!$A$2:$A$5000&amp;""))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>※ 商品券は売上に含まれています（後で換金されるため）。枚数は換金額の確認用です。</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="B19" s="14" t="inlineStr">
+    <row r="22">
+      <c r="B22" s="14" t="inlineStr">
         <is>
           <t>※ 各iPadの「履歴・集計」画面の総売上を足した金額と、上の総売上が一致するか必ず確認してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>※ 現金の実額 = 総売上 − PayPay − 未納 − 商品券の換金額</t>
         </is>
       </c>
     </row>
@@ -975,7 +1027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M4"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -991,6 +1043,8 @@
     <col width="11" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1059,6 +1113,16 @@
           <t>商品券</t>
         </is>
       </c>
+      <c r="N1" s="20" t="inlineStr">
+        <is>
+          <t>支払い</t>
+        </is>
+      </c>
+      <c r="O1" s="20" t="inlineStr">
+        <is>
+          <t>職員名</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
